--- a/sheets/조재수대금교본/검수/약속-2.xlsx
+++ b/sheets/조재수대금교본/검수/약속-2.xlsx
@@ -2803,7 +2803,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㅅ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="E3" s="22"/>
@@ -2846,23 +2846,11 @@
       <c r="E4" s="23"/>
       <c r="F4" s="21"/>
       <c r="G4" s="23"/>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H4" s="21"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J4" s="21"/>
       <c r="K4" s="23"/>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L4" s="21"/>
       <c r="M4" s="23"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
@@ -2945,18 +2933,9 @@
     </row>
     <row r="7" ht="90.2" customHeight="true">
       <c r="A7" s="0"/>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="B7" s="21"/>
       <c r="C7" s="23"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D7" s="21"/>
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
@@ -3048,7 +3027,7 @@
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㅅ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G9" s="22"/>
@@ -3085,29 +3064,13 @@
       <c r="E10" s="23"/>
       <c r="F10" s="21"/>
       <c r="G10" s="23"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="23"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="23"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="23"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N10" s="21"/>
       <c r="O10" s="23"/>
     </row>
     <row r="11" ht="90.2" customHeight="true">
@@ -3154,8 +3117,7 @@
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-㳞
-‹</t>
+㳞</t>
         </is>
       </c>
       <c r="E12" s="22"/>
@@ -3190,11 +3152,7 @@
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">∧ㄱ</t>
-        </is>
-      </c>
+      <c r="D13" s="21"/>
       <c r="E13" s="23"/>
       <c r="F13" s="21"/>
       <c r="G13" s="23"/>
@@ -3234,11 +3192,7 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/약속-2.xlsx
+++ b/sheets/조재수대금교본/검수/약속-2.xlsx
@@ -2803,7 +2803,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㅅ</t>
         </is>
       </c>
       <c r="E3" s="22"/>
@@ -2933,7 +2933,11 @@
     </row>
     <row r="7" ht="90.2" customHeight="true">
       <c r="A7" s="0"/>
-      <c r="B7" s="21"/>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="C7" s="23"/>
       <c r="D7" s="21"/>
       <c r="E7" s="23"/>
@@ -3027,7 +3031,7 @@
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㅅ</t>
         </is>
       </c>
       <c r="G9" s="22"/>
@@ -3152,7 +3156,11 @@
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
-      <c r="D13" s="21"/>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">∧ㄱ</t>
+        </is>
+      </c>
       <c r="E13" s="23"/>
       <c r="F13" s="21"/>
       <c r="G13" s="23"/>

--- a/sheets/조재수대금교본/검수/약속-2.xlsx
+++ b/sheets/조재수대금교본/검수/약속-2.xlsx
@@ -2757,26 +2757,26 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="56.34" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="83.81" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21"/>
       <c r="C3" s="22"/>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="O3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="83.81" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="O4" s="23"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="83.81" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O5" s="24"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="83.81" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="O6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="83.81" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
       <c r="N7" s="21"/>
       <c r="O7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="83.81" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="O8" s="24"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="83.81" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="O9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="83.81" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -3077,7 +3077,7 @@
       <c r="N10" s="21"/>
       <c r="O10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="83.81" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="O11" s="24"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="83.81" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="83.81" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="83.81" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3237,6 +3237,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="71"/>
 </worksheet>
 </file>